--- a/data/quiz/quiz_bank.xlsx
+++ b/data/quiz/quiz_bank.xlsx
@@ -532,32 +532,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>どの大学の研究チームが「アメリカ人が時間をどう使ってるか調査」を分析した？</t>
+          <t>記事が紹介する調査で分かった、実際にお金の管理に使われている時間の特徴は？</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ハーバード大学</t>
+          <t>娯楽や仕事と比べてわずかしか使われていない</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>サラゴサ大学</t>
+          <t>娯楽よりも多くの時間が使われている</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>スタンフォード大学</t>
+          <t>仕事とほぼ同じ時間が使われている</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>オックスフォード大学</t>
+          <t>誰もが十分な時間を使っている</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -595,27 +595,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>この調査の対象者数は何人だった？</t>
+          <t>調査で、お金の管理をしている人の多くはどう感じていたか？</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>約1万9千人</t>
+          <t>楽しく取り組んでいた</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>約19万人</t>
+          <t>嫌いで幸福感が低かった</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>約190万人</t>
+          <t>特に何も感じていなかった</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>約1900人</t>
+          <t>むしろ達成感を得ていた</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -658,27 +658,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>アメリカ人が1日平均でお金の管理に使う時間は？</t>
+          <t>この記事のタイトルが投げかけている問いは何か？</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>約8.3分</t>
+          <t>なぜお金持ちほど時間をかけるのにストレスが少ないのか</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>約38分</t>
+          <t>なぜ誰もがお金の管理を嫌うのか</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>約83分</t>
+          <t>なぜ仕事より娯楽が優先されるのか</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>約3分</t>
+          <t>なぜ調査対象が偏っているのか</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -721,32 +721,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>同調査で娯楽に使われていた1日の平均時間は？</t>
+          <t>この記事から読み取れる実践的な示唆は？</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>約128分</t>
+          <t>お金の管理にかける時間を増やせば必ずストレスが減る</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>約228分</t>
+          <t>お金の管理へのストレスは時間の長さだけでは説明できなさそうだ</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>約342分</t>
+          <t>お金の管理は他人に任せるべきだ</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>約42分</t>
+          <t>娯楽の時間をすべてお金の管理に回すべきだ</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -784,27 +784,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>この記事が更年期サプリ情報のベースにしている研究者は？</t>
+          <t>更年期の症状を抑える方法として、記事が最有力としているのは？</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>モンタナ州立大学のアンダーソン先生</t>
+          <t>ホルモン補充療法</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ハーバード大学のスミス先生</t>
+          <t>サプリメント全般</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>東京大学の田中先生</t>
+          <t>運動療法</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>スタンフォード大学のリー先生</t>
+          <t>漢方薬全般</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ホットフラッシュや膣の乾燥に対して「効果は小さいが比較的データが多い」とされた成分は？</t>
+          <t>大豆イソフラボンについて記事が示した評価は？</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ブラックコホシュ</t>
+          <t>効果は大きくデータも豊富</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>大豆イソフラボン</t>
+          <t>効果は小さいが比較的データが多い</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>葛</t>
+          <t>効果は不明でデータもない</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>レッドクローバー</t>
+          <t>明確な悪影響が確認されている</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -910,32 +910,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>寝汗など一部の更年期症状に対し「結果が割れている」とされた成分は？</t>
+          <t>レッドクローバーについての評価は？</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>大豆イソフラボン</t>
+          <t>効果が明確に確認されている</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>葛</t>
+          <t>結果が割れている</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>レッドクローバー</t>
+          <t>データが豊富で信頼できる</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ブラックコホシュ</t>
+          <t>全く効果がないと証明されている</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -973,32 +973,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>「データ不足」と評価された成分は？</t>
+          <t>この記事全体が伝えようとしているサプリ選びの姿勢として適切なのは？</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>葛</t>
+          <t>どのサプリも同じくらい効果があるので何でもよい</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>大豆イソフラボン</t>
+          <t>成分ごとにエビデンスの強さが異なるので見極めが必要</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>レッドクローバー</t>
+          <t>サプリより必ずホルモン補充療法を優先すべき</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ブラックコホシュ</t>
+          <t>エビデンスがなくても人気の成分を選べばよい</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1036,32 +1036,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>この研究を行ったのはどこの大学？</t>
+          <t>記事が紹介する研究が出した結論は？</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>コンスタンツ大学</t>
+          <t>完全在宅の方が生産性が高い</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>チューリッヒ大学</t>
+          <t>出勤で得られる「雑談」の喪失が在宅勤務のメリットを上回る</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ケンブリッジ大学</t>
+          <t>出社と在宅に生産性の差はない</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>サラゴサ大学</t>
+          <t>在宅勤務は職場への帰属意識を必ず高める</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>研究で「出勤における最大のメリット」とされたものは？</t>
+          <t>記事が出勤の最大のメリットとして挙げているものは？</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>通勤運動</t>
+          <t>通勤時間の有効活用</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>昇給</t>
+          <t>上司からの直接指導</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>集中力向上</t>
+          <t>オフィス設備の利用</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1162,27 +1162,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>研究対象はどんな働き方をしている会社員か？</t>
+          <t>この研究が対象としたのはどんな働き方をしている人たちか？</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>完全在宅勤務者</t>
+          <t>完全在宅勤務者のみ</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>完全出社勤務者</t>
+          <t>完全出社勤務者のみ</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>ハイブリッド勤務者</t>
+          <t>ハイブリッド勤務をしている会社員</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>フリーランス</t>
+          <t>フリーランスの会社員</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1225,32 +1225,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>記事によれば、出勤で得られる雑談を失うデメリットは在宅勤務のメリットと比べてどうだったか？</t>
+          <t>記事の内容から導ける実践的な示唆は？</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>デメリットの方が上回った</t>
+          <t>在宅勤務は生産性の面で完全に劣るので廃止すべき</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>メリットの方が上回った</t>
+          <t>雑談のような偶発的な交流の価値を軽視すべきではない</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>ちょうど釣り合った</t>
+          <t>出社日はすべて雑談に費やすべき</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>比較されていない</t>
+          <t>生産性は働き方に関係なく一定である</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1288,27 +1288,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>新しく始まった無料メール配信の名称は？</t>
+          <t>この新しい配信サービスが解決しようとしている読者の悩みは？</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>パレオな男 週刊</t>
+          <t>記事が少なすぎること</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>パレオな男 ダイジェスト</t>
+          <t>更新が多く気になる記事を見逃してしまうこと</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>パレオな男 まとめ</t>
+          <t>記事が難しすぎること</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>パレオな男 ニュースレター</t>
+          <t>広告が多すぎること</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1351,32 +1351,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>このダイジェストは何曜日に配信される？</t>
+          <t>「パレオな男 ダイジェスト」が届けてくれる内容は？</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>毎週月曜日</t>
+          <t>過去1年分のベスト記事</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>毎週金曜日</t>
+          <t>前の週に公開された記事のまとめ</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>毎週日曜日</t>
+          <t>読者投票で選ばれた記事</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>毎週水曜日</t>
+          <t>海外ニュースの翻訳記事</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>配信内容は何のまとめか？</t>
+          <t>このダイジェストの配信頻度は？</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>前の週に公開した記事</t>
+          <t>毎日</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>過去1年分の人気記事</t>
+          <t>週1回</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>読者から寄せられた質問</t>
+          <t>月1回</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>DaiGoの生放送内容</t>
+          <t>隔週</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1477,32 +1477,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>このお知らせが出された理由として挙げられていたことは？</t>
+          <t>記事が示唆する、忙しい読者にとってのこのサービスのメリットは？</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ブログを閉鎖するため</t>
+          <t>情報を後で読もうとして忘れてしまう問題を減らせる</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>更新が多く記事を見逃してしまう悩みが多かったため</t>
+          <t>ブログを読む必要がなくなる</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>広告収入を増やすため</t>
+          <t>記事の内容が要約されて短くなる</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>海外展開のため</t>
+          <t>有料会員限定の記事が読めるようになる</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1540,32 +1540,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>セフレ関係を英語で何と呼ぶ(略称)？</t>
+          <t>このメタ分析が比較したのは、セフレ関係と何か？</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ONS</t>
+          <t>恋人がいる人や独身者との関係</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FWB</t>
+          <t>夫婦関係のみ</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>同性間の関係のみ</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>オンラインでの関係のみ</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1603,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>メタ分析で扱われた研究の件数は？</t>
+          <t>分析の結果、セフレ関係にはどんな両面があるとされたか？</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18件</t>
+          <t>気楽で安全な面と健康上のリスクが高い面</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25件</t>
+          <t>経済的な安定と不安定</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>38件</t>
+          <t>長続きする面と短命な面のみ</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>52件</t>
+          <t>社会的に評価が高い面と低い面のみ</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>分析で比較された5項目に含まれないものは？</t>
+          <t>記事が調べた項目に含まれないものは？</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>年収の違い</t>
+          <t>仕事のパフォーマンス</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1729,32 +1729,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>分析結果、セフレ関係にはどんな両面があるとされたか？</t>
+          <t>この記事全体が伝えている、セフレ関係についての見方として適切なのは？</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>気楽で安全な面と健康上のリスクが高い面</t>
+          <t>単純に悪いものだと結論づけている</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>経済的メリットとデメリット</t>
+          <t>単純に良いものだと結論づけている</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>長期的な安定と短期的な不安定</t>
+          <t>メリットとリスクの両方がある複雑なものとして描いている</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>社会的評価の高さと低さ</t>
+          <t>全く違いがないとしている</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1792,32 +1792,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>このシリーズが参考にしている、スーパーエイジャー研究で有名な研究者は？</t>
+          <t>この記事のテーマ「人間関係は『量』より『機能』で考えよう」が意味することとして適切なのは？</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>トポル先生</t>
+          <t>友人の数を増やすことが最も重要</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>アンダーソン先生</t>
+          <t>関係の数より、その関係が果たす役割の方が重要</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>ロミゼフスキー氏</t>
+          <t>人間関係は健康と無関係</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ウィリソン氏</t>
+          <t>孤独は問題にならない</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>トポル先生が提唱する考え方の名称は？</t>
+          <t>Lifestyle+という考え方で、食事・運動・睡眠に加えて重視されている要素は？</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Lifestyle+</t>
+          <t>収入</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Health Boost</t>
+          <t>社会的孤立と孤独</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Aging Well</t>
+          <t>学歴</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Vitality Plan</t>
+          <t>住環境</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>今回のテーマは何についてか？</t>
+          <t>記事が最初に押さえておくべきとしているポイントは？</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>食事管理</t>
+          <t>孤独と社会的孤立は同じ意味である</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>運動習慣</t>
+          <t>孤独と社会的孤立は同じではない</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>孤独対策</t>
+          <t>孤独は誰にでも起きるものではない</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>睡眠の質</t>
+          <t>社会的孤立は健康に影響しない</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1981,27 +1981,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lifestyle+で食事・運動・睡眠に加えて扱われている要素は？</t>
+          <t>この記事が読者に促している行動として適切なのは？</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>収入</t>
+          <t>友人の数を数えて増やす努力をする</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>社会的孤立と孤独</t>
+          <t>人間関係の「機能」に目を向けて孤独対策を考える</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>学歴</t>
+          <t>一人で過ごす時間を完全になくす</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>住環境</t>
+          <t>SNSのフォロワーを増やす</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2044,27 +2044,27 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>分析に使われたデータは何と呼ばれる調査か？</t>
+          <t>この記事が調べようとしたテーマは？</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>世界価値観調査</t>
+          <t>恋人がいる人といない人にどんな特徴の違いがあるか</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>世界幸福度調査</t>
+          <t>結婚した方が幸せかどうか</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>国際労働調査</t>
+          <t>恋愛にお金がどれくらいかかるか</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>世界健康調査</t>
+          <t>SNSが恋愛に与える影響</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2107,32 +2107,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>この調査を行ったのはどこの大学？</t>
+          <t>分析で比較に使われた要因に含まれないものは？</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ヴロツワフ大学</t>
+          <t>年齢や性別</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>ワルシャワ大学</t>
+          <t>学歴や収入</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ウィーン大学</t>
+          <t>仕事の有無</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ベルリン大学</t>
+          <t>血液型</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -2170,32 +2170,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>分析対象となったデータの人数はおよそ何人？</t>
+          <t>記事の冒頭で紹介されている、恋愛にまつわるよくある俗説は？</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>約7,100人</t>
+          <t>収入があればモテる、コミュ力があればいい</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>約71,000人</t>
+          <t>顔が良ければ必ずモテる</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>約710,000人</t>
+          <t>若ければ若いほどモテる</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>約7,100,000人</t>
+          <t>学歴が高いほどモテる</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2233,32 +2233,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>調査データはどの期間に集められたものか？</t>
+          <t>この記事が伝えようとしていることは？</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2010〜2014年</t>
+          <t>個人のスペックだけでは恋人の有無を十分に説明できない可能性がある</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2013〜2017年</t>
+          <t>収入さえあれば必ず恋人ができる</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2017〜2021年</t>
+          <t>恋人ができるかどうかは完全に運で決まる</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2020〜2024年</t>
+          <t>文化の違いは恋愛に一切関係ない</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2296,32 +2296,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>この記事でAIの広告作成能力を評価するのに使われたフレームワークは？</t>
+          <t>記事によれば、一般的な画像生成AIが苦手とすることは？</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AIDA</t>
+          <t>綺麗な画像を作ること</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SWOT</t>
+          <t>消費者の購買意欲を刺激する広告を作ること</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>PDCA</t>
+          <t>文字を含む画像を作ること</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>高解像度の画像を作ること</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2359,27 +2359,27 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>AIDAの4段階に含まれないものは？</t>
+          <t>研究チームが広告効果を測るために採用したフレームワークは4段階に分かれるが、含まれないものは？</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>注意を引く</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>興味を持たせる</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Desire</t>
+          <t>欲しいと思わせる</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Loyalty</t>
+          <t>忘れさせる</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2422,27 +2422,27 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>研究チームが収集したオンライン広告の点数はおよそ何点？</t>
+          <t>記事の結論として、画像生成AIが「売れる広告」を作るコツをどうできるとされたか？</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2万1千点</t>
+          <t>学習させることは不可能</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>21万点</t>
+          <t>学習することができる</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>210万点</t>
+          <t>人間には決して再現できない</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2,100点</t>
+          <t>広告業界では使えない</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2485,27 +2485,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>記事によれば、一般的な画像生成AIは何を学習していないとされたか？</t>
+          <t>この記事が示す実践的な意味として適切なのは？</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>デザインのトレンド</t>
+          <t>AIに広告を作らせても効果は期待できない</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>消費者心理</t>
+          <t>適切な工夫をすればAIは効果的な広告を作れる可能性がある</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>色彩理論</t>
+          <t>AI生成広告は必ず人間の作った広告に劣る</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ブランドロゴ</t>
+          <t>広告作成にAIを使うのは違法である</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2548,32 +2548,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>この新商品を発売したブランドは？</t>
+          <t>記事が説明する「状態ノイズ」とは何か？</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PALEO LABO</t>
+          <t>香水の匂いが強すぎること</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Dラボコスメ</t>
+          <t>ニオイや汗、ベタつき、乾燥などの小さな違和感が重なって脳のメモリを奪うもの</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>パレオビューティー</t>
+          <t>スマホの通知が多すぎること</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>DaiGo Labs</t>
+          <t>睡眠不足による集中力低下</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2611,32 +2611,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>商品コンセプトとして挙げられている、脳のメモリを奪う要因の呼び名は？</t>
+          <t>EVER CLEANが状態ノイズを減らすために採用しているアプローチは？</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>状態ノイズ</t>
+          <t>強い香りでニオイを隠す</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>体調シグナル</t>
+          <t>肌のコンディションを整える</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>感覚疲労</t>
+          <t>冷却スプレーで一時的にごまかす</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>身体ストレス</t>
+          <t>制汗成分だけを強化する</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2674,32 +2674,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>EVER CLEANが目指しているのは何によって状態ノイズを減らすことか？</t>
+          <t>記事によれば、肌の乾燥はどんな影響を与えるとされているか？</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>強い香りでニオイを隠す</t>
+          <t>状態ノイズの大きな原因になる</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>肌のコンディションを整える</t>
+          <t>状態ノイズには関係ない</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>冷感成分で刺激を与える</t>
+          <t>むしろ状態ノイズを減らす</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>防臭シートを併用する</t>
+          <t>記事では触れられていない</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2737,32 +2737,32 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>前回のエントリで語られていたテーマは？</t>
+          <t>この記事が伝えたい商品コンセプトの核は？</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>商品の価格設定</t>
+          <t>香りでごまかすのではなく違和感の原因そのものを減らす</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>EVER CLEANのコンセプト</t>
+          <t>とにかく強い香りをつける</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>発売イベントの告知</t>
+          <t>価格を下げることが最優先</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>競合製品との比較</t>
+          <t>見た目のパッケージデザインが重要</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2800,27 +2800,27 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>今回のテーマは何についてか？</t>
+          <t>記事によれば、慢性的なストレスが促進するとされるものは？</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>食事の質</t>
+          <t>骨密度の向上</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ストレス対策</t>
+          <t>がんの進行や転移</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>運動強度</t>
+          <t>筋力の維持</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>睡眠時間</t>
+          <t>記憶力の向上</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2863,27 +2863,27 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>記事によれば、慢性的なストレスが促進するとされるものは？</t>
+          <t>記事はストレスをどう分類しているか？</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>がんの進行や転移</t>
+          <t>良いストレスと悪いストレスの2種類</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>骨密度の向上</t>
+          <t>完全に1種類しかない</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>筋力の維持</t>
+          <t>4段階のレベルに分類</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>視力の改善</t>
+          <t>年齢別に分類</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2926,32 +2926,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>記事はストレスを大きく何種類に分けているか？</t>
+          <t>このシリーズが健康寿命に関わる要素として重視しているものに、ストレス対策以外で含まれるのは？</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1種類</t>
+          <t>食事・運動・睡眠</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2種類</t>
+          <t>収入・学歴</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>3種類</t>
+          <t>居住地域</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>4種類</t>
+          <t>家族構成</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2989,27 +2989,27 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>このシリーズの元になっている考え方は？</t>
+          <t>この記事のタイトルが示す重要なポイントは？</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Lifestyle+</t>
+          <t>同じストレス対策でも人によって効き方が違う</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Wellness Score</t>
+          <t>ストレス対策は誰にでも同じ効果がある</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Aging Index</t>
+          <t>ストレスは常に悪いものである</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Stress Map</t>
+          <t>ストレス対策は不要である</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3052,32 +3052,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>じゃがいもを水にさらすと減らせるとされる物質は？</t>
+          <t>じゃがいもを水にさらす理由として、記事が新たに強調しているのは？</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>アクリルアミド</t>
+          <t>くっつき防止だけ</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>アクロレイン</t>
+          <t>変色防止だけ</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ヒスタミン</t>
+          <t>揚げたときにできるアクリルアミドを減らすこと</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ソラニン</t>
+          <t>味を良くするため</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3115,27 +3115,27 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>アクリルアミドは何と何が高温で反応してできるか？</t>
+          <t>記事によれば、冷蔵庫で保存したじゃがいもはどうするのが良いとされるか？</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>アスパラギンと還元糖</t>
+          <t>揚げ物に向かない</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>グルテンと水</t>
+          <t>揚げ物に最適</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>脂質とタンパク質</t>
+          <t>生食に向かない</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ビタミンCと鉄分</t>
+          <t>特に違いはない</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>記事の根拠として挙げられている機関は？</t>
+          <t>記事が勧める揚げ色の目安は？</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>厚生労働省とWHO</t>
+          <t>濃い茶色までしっかり揚げる</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>農林水産省と米国FDA</t>
+          <t>薄い黄金色で止める</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>消費者庁とEU</t>
+          <t>白いままで揚げるのをやめる</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>環境省とCDC</t>
+          <t>黒っぽくなるまで揚げる</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3241,27 +3241,27 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>記事が勧める揚げ色の目安は？</t>
+          <t>この記事から得られる調理上の実践的な教訓は？</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>濃い茶色</t>
+          <t>水にさらす工程は省いても問題ない</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>薄い黄金色</t>
+          <t>水にさらす、保存状態、揚げ色の3点に気を配ると安全性が上がる</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>真っ黒に近い色</t>
+          <t>じゃがいもは揚げずに食べるべき</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>白っぽい色のまま</t>
+          <t>冷蔵庫で長期保存するほど良い</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3304,32 +3304,32 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>イカが丸まって硬くなる主な原因とされる部位は？</t>
+          <t>イカが加熱すると丸まって硬くなる主な理由は？</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>皮の第1層</t>
+          <t>むいたつもりでも皮の一部(第3・4層)が身に残っているから</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>皮の第2層</t>
+          <t>塩をかけすぎているから</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>皮の第3層</t>
+          <t>加熱時間が短すぎるから</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>皮の第4層</t>
+          <t>イカの種類によるもので対策はない</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3367,32 +3367,32 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>記事が参照している資料は？</t>
+          <t>手でつるんとむける皮は何層目までとされているか？</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>全国いか加工業協同組合「イカ学Q&amp;A60」</t>
+          <t>第1層まで</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>水産庁「イカ白書」</t>
+          <t>第2層まで</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>日本かまぼこ協会資料</t>
+          <t>第3層まで</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>農林水産省「魚介類ガイド」</t>
+          <t>第4層まで</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3430,27 +3430,27 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>手でむける茶色い皮は何層目までか？</t>
+          <t>記事によれば、身に密着したまま残りやすい層はどこか？</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>第1層まで</t>
+          <t>第1層・第2層</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>第2層まで</t>
+          <t>第3層・第4層</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>第3層まで</t>
+          <t>全層とも簡単にむける</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>第4層まで</t>
+          <t>どの層も残らない</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3493,32 +3493,32 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>第4層はどの方向に走る繊維性の組織か？</t>
+          <t>この記事が示す実践的な対策は？</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>胴の横方向</t>
+          <t>切り込みを入れることでやわらかく仕上げる</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>胴の縦方向(体軸方向)</t>
+          <t>皮は一切むかずに調理する</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>らせん状</t>
+          <t>加熱時間を大幅に延ばす</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>放射状</t>
+          <t>冷凍してから調理する</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3556,27 +3556,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>焼き鮭の表面に出る白いかたまりの正体は？</t>
+          <t>焼き鮭に出る白いかたまりの正体として記事が説明しているのは？</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>コラーゲン</t>
+          <t>傷んで腐り始めているサイン</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>アルブミン</t>
+          <t>水溶性たんぱく質「アルブミン」</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>ケラチン</t>
+          <t>焼きすぎで炭化した部分</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ミオシン</t>
+          <t>添加物の結晶</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3619,27 +3619,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>アルブミンと同じ仲間とされるものは？</t>
+          <t>記事によれば、あの白い汁は食べても問題があるか？</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>卵白</t>
+          <t>無害で食べても問題ない</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>牛乳のカゼイン</t>
+          <t>有害なので取り除くべき</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>大豆のグリシニン</t>
+          <t>アレルギーの原因になる</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>米のグルテリン</t>
+          <t>必ず腐敗のサインである</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3682,32 +3682,32 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>アルブミンが押し出されて固まり始めるのはおよそ何度以上か？</t>
+          <t>白い汁が出るのを防ぐために記事が勧める方法は？</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>45℃以上</t>
+          <t>焼く前に塩水に10分浸ける</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>55℃以上</t>
+          <t>焼いた後に塩を振る</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>65℃以上</t>
+          <t>冷凍したまま焼く</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>85℃以上</t>
+          <t>強火で一気に焼き上げる</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3745,32 +3745,32 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>記事が勧める白い汁の予防策は？</t>
+          <t>この記事が伝える調理科学の教訓として適切なのは？</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>焼く前に砂糖をまぶす</t>
+          <t>見た目が気になる現象でも仕組みを知れば対処法が分かる</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>焼く前に塩水に10分浸ける</t>
+          <t>白い汁が出たら必ず失敗作である</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>冷凍してから焼く</t>
+          <t>魚は加熱しないほうがよい</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>強火で一気に焼く</t>
+          <t>白い汁は完全に防ぐことはできない</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3808,32 +3808,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>重曹の化学的な正体は？</t>
+          <t>重曹が生地を膨らませる仕組みとして記事が説明しているのは？</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>炭酸水素ナトリウム</t>
+          <t>熱だけで膨張する</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>炭酸カルシウム</t>
+          <t>酸と反応して二酸化炭素が発生し生地を押し広げる</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>塩化ナトリウム</t>
+          <t>水分を吸収して膨張する</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>水酸化ナトリウム</t>
+          <t>発酵によって膨らむ</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3871,32 +3871,32 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>重曹が膨らむ反応を起こすために組ませる必要があるものは？</t>
+          <t>重曹を酸と組ませずに加熱だけで使うと生地に何が残るとされるか？</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>塩</t>
+          <t>炭酸ナトリウム</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>酸</t>
+          <t>クエン酸</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>油</t>
+          <t>重炭酸カリウム</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>砂糖</t>
+          <t>硫酸ナトリウム</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3934,32 +3934,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>重曹を加熱だけで分解させると生地に残り、苦みや黄色っぽさの原因になる物質は？</t>
+          <t>重曹だけで作った生地の特徴として記事が挙げているのは？</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>炭酸ナトリウム</t>
+          <t>焼き色が薄く膨らみが良い</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>クエン酸ナトリウム</t>
+          <t>焼き色が濃く独特の苦みや黄色っぽさが出る</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>重炭酸カリウム</t>
+          <t>味に全く変化がない</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>硫酸ナトリウム</t>
+          <t>膨らみすぎて崩れる</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3997,32 +3997,32 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>記事で重曹を使ったパンケーキがふわっと軽くなる例として挙げられていた食材は？</t>
+          <t>この記事から得られる実践的な教訓は？</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>レモン汁</t>
+          <t>ベーキングパウダーの代わりに重曹を使うときは酸性の材料と組み合わせるとよい</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>ヨーグルト</t>
+          <t>重曹はどんな生地にも単独で使うのが正解</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>炭酸水</t>
+          <t>重曹は加熱すると必ず美味しくなる</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>はちみつ</t>
+          <t>重曹と酸は絶対に組み合わせてはいけない</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -4060,27 +4060,27 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>豆乳が固まる際に働く豆腐凝固剤として記事で挙げられているものは？</t>
+          <t>豆乳が液体のままでいられる理由として記事が説明しているのは？</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>にがり</t>
+          <t>たんぱく質の粒子がマイナスに帯電し反発し合っているから</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>酢</t>
+          <t>水分量が非常に多いから</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>塩</t>
+          <t>加熱されていないから</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>砂糖</t>
+          <t>大豆の油分が多いから</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4123,32 +4123,32 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>にがりの主成分は？</t>
+          <t>にがりが豆乳を固める仕組みとして記事が説明しているのは？</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>塩化マグネシウム</t>
+          <t>水分を蒸発させる</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>塩化カルシウム</t>
+          <t>プラス電荷のマグネシウムイオンが粒子の反発を打ち消し凝集させる</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>硫酸マグネシウム</t>
+          <t>高温で加熱してたんぱく質を壊す</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>炭酸ナトリウム</t>
+          <t>酵素の働きでたんぱく質を分解する</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4186,32 +4186,32 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>豆乳中の大豆たんぱく質として記事に挙げられている名称は？</t>
+          <t>家庭で豆腐を作る際に、記事が使うことを勧めている調理器具は？</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>グリシニンとβ-コングリシニン</t>
+          <t>圧力鍋</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>カゼインとホエー</t>
+          <t>電子レンジ</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>グルテニンとグリアジン</t>
+          <t>オーブン</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>アルブミンとグロブリン</t>
+          <t>蒸し器</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4249,27 +4249,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>豆乳の粒子が液体中でバラバラでいられる理由として挙げられていたのは？</t>
+          <t>この記事が伝えている料理科学の面白さとして適切なのは？</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>粒子表面がマイナスに帯電し反発するため</t>
+          <t>身近な化学反応を理解すれば専門店でなくても再現できる</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>粒子が非常に軽いため</t>
+          <t>豆腐作りには専門的な設備が絶対に必要</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>水温が低いため</t>
+          <t>にがりを使わなくても豆乳は固まる</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>粒子にコーティングがあるため</t>
+          <t>豆乳を固めるには加熱以外の方法はない</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4312,27 +4312,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>記事によれば、ケージ卵の特徴とされたのは？</t>
+          <t>この週の記事群に共通していた総括テーマは？</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>うま味と甘みが強い</t>
+          <t>調理器具の性能が味を決める</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>コクが強い</t>
+          <t>同じ材料でも周りの条件が味や栄養を変える</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>色が濃い</t>
+          <t>高価な食材ほど美味しい</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>殻が厚い</t>
+          <t>レシピの複雑さが美味しさを決める</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>平飼い卵の特徴とされたのは？</t>
+          <t>ケージ卵の特徴として紹介されているのは？</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>保存期間が長い</t>
+          <t>保存期間が短い</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -4438,27 +4438,27 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>この週刊まとめが対象としている期間は？</t>
+          <t>平飼い卵の特徴として紹介されているのは？</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026年8月17日〜23日</t>
+          <t>コクが強い</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026年8月24日〜30日</t>
+          <t>うま味と甘みが強い</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026年9月1日〜7日</t>
+          <t>色が薄い</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026年7月24日〜30日</t>
+          <t>殻が厚い</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4501,27 +4501,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>記事の総括で述べられていた共通テーマは？</t>
+          <t>記事の総括で「台所で一番安く試せる変数」として示唆されているのは？</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>調理器具の進化</t>
+          <t>高価な調理器具を買うこと</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>同じ材料でもまわりの条件が味と栄養を変える</t>
+          <t>料理そのものではなく料理の前後にある環境</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>産地による味の違い</t>
+          <t>レシピ本を買うこと</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>価格高騰の影響</t>
+          <t>食材を高級品に変えること</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4564,22 +4564,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>チーズソースが分離してザラザラになる主な原因とされるのは？</t>
+          <t>チーズソースがザラザラに分離する主な原因として記事が指摘しているのは？</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>チーズが古いこと</t>
+          <t>チーズの品質</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>火の強さ</t>
+          <t>火の強さ(加熱しすぎ)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>混ぜ方が足りないこと</t>
+          <t>混ぜる道具</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4627,32 +4627,32 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>牛乳の主役たんぱく質として挙げられているのは？</t>
+          <t>チーズの網目構造をつなぐ「接着剤」の役割を果たしている成分は？</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>カゼイン</t>
+          <t>脂肪球</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>アルブミン</t>
+          <t>リン酸カルシウム</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>ラクトフェリン</t>
+          <t>水分</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ラクトース</t>
+          <t>乳糖</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4690,32 +4690,32 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>カゼインの網目構造をつなぐ「接着剤」とされる成分は？</t>
+          <t>チーズが加熱で溶ける性質(メルト性)を左右する要因として記事が挙げているのは？</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>脂肪球</t>
+          <t>接着剤(リン酸カルシウム)がどれだけ残っているか</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>リン酸カルシウム</t>
+          <t>チーズの色</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>水分</t>
+          <t>塩分濃度のみ</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>乳糖</t>
+          <t>賞味期限</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -4753,27 +4753,27 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>記事で解説者として紹介されているのは？</t>
+          <t>この記事から得られる調理の実践的な教訓は？</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>雪印メグミルクの堂迫俊一博士</t>
+          <t>チーズソースは火を止めてから溶かすと分離を防ぎやすい</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>明治乳業の田中博士</t>
+          <t>チーズは強火で一気に溶かすべき</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>森永乳業の鈴木博士</t>
+          <t>チーズソースは分離しても問題ない</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>農研機構の佐藤博士</t>
+          <t>カゼインを増やせば必ず分離しなくなる</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>記事によれば、野菜は収穫後どうなるか？</t>
+          <t>記事によれば、野菜は収穫された後どうなっているか？</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>呼吸を続け酵素が働き続ける</t>
+          <t>呼吸を続け酵素が働き続けている</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>完全に水分を失う</t>
+          <t>完全に休眠状態になる</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>糖度が上がり続ける</t>
+          <t>栄養価が増加し続ける</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4879,32 +4879,32 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>記事で不安定で分解が進みやすい成分として挙げられているのは？</t>
+          <t>ビタミンCのような不安定な成分が分解される条件として挙げられていないものは？</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ビタミンC</t>
+          <t>光にさらされる</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>食物繊維</t>
+          <t>高温にさらされる</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>カリウム</t>
+          <t>酸素にさらされる</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>脂質</t>
+          <t>冷凍保存される</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -4942,32 +4942,32 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>分解が速まる条件として挙げられていないものは？</t>
+          <t>記事が「冷凍野菜」を表現する言い方として使っているのは？</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>光にさらされる</t>
+          <t>栄養の時計が畑で止まっている</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>高温にさらされる</t>
+          <t>生野菜より必ず劣化している</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>酸素にさらされる</t>
+          <t>手抜き料理の代表</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>冷凍保存されること</t>
+          <t>加工中に栄養が失われる</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5005,32 +5005,32 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>記事の主張は冷凍野菜についてどんなものか？</t>
+          <t>この記事が伝えたい、冷凍野菜に対する見方の転換は？</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>手抜きであり栄養価は低い</t>
+          <t>冷凍野菜は手抜きで栄養も劣るという先入観を見直すべき</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>手抜きではなく栄養の時計が畑で止まっている</t>
+          <t>生野菜は常に冷凍野菜より優れている</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>生野菜より必ず不味い</t>
+          <t>冷凍野菜は生野菜より必ず栄養価が高い</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>加工中に栄養が失われる</t>
+          <t>保存方法によって栄養価は変わらない</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5068,32 +5068,32 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>しょうがの辛味成分の「主役」とされるのは？</t>
+          <t>しょうがに関する「加熱すると体を温める力が強くなる」という通説について、記事が示した実際の研究結果は？</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ジンゲロール</t>
+          <t>通説通り加熱で大きく変化する</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>ショウガオール</t>
+          <t>家庭の煮る・蒸す程度の加熱ではほとんど変化しない</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>カプサイシン</t>
+          <t>加熱すると逆に辛味が完全になくなる</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ピペリン</t>
+          <t>生のしょうがには温め成分が全くない</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>加熱で生成されるとされる、体を温める成分は？</t>
+          <t>しょうがの辛味の主役とされる成分は？</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>クルクミン</t>
+          <t>カプサイシン</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5194,27 +5194,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>記事のタイトルにある「98対2」は何の比率を表すか？</t>
+          <t>この記事が「がっかりする話ではなくむしろ実用的な情報」だとしている理由は？</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>生しょうがのジンゲロールとショウガオールの比率</t>
+          <t>加熱しなければならないという縛りがなくなるから</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>加熱前後の重量比</t>
+          <t>しょうがを一切使わなくてよくなるから</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>辛味と甘味の比率</t>
+          <t>加熱すれば必ず効果が上がると分かったから</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>水分と繊維の比率</t>
+          <t>高価なしょうがを買う必要がなくなるから</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5257,27 +5257,27 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>記事の結論として、家庭の煮る・蒸す程度の加熱でジンゲロールがショウガオールに変わる量は？</t>
+          <t>この記事から得られる実践的な教訓は？</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ほとんど変化しない</t>
+          <t>生のしょうがのままでも『温め成分』の観点では大差ない使い方ができる</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>半分近くまで変わる</t>
+          <t>しょうがは必ず長時間煮込む必要がある</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>ほぼ全て変わる</t>
+          <t>しょうがは加熱すると栄養がすべて失われる</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>3割程度変わる</t>
+          <t>しょうがを加熱すると別の食品になる</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5320,32 +5320,32 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ヨーグルトの表面に出る透明な液体の名前は？</t>
+          <t>ヨーグルトの表面に出る透明な液体の正体は？</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ホエー(乳清)</t>
+          <t>傷んで出てきた腐敗液</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>カード</t>
+          <t>牛乳の栄養が溶け込んだホエー(乳清)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>ラクトース液</t>
+          <t>添加された保存料</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>乳脂肪分離液</t>
+          <t>単なる水分で栄養はない</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5383,32 +5383,32 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>このホエーは何の栄養が溶け込んだものとされているか？</t>
+          <t>記事は、あの液体をどう扱うことを勧めているか？</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>牛乳の栄養</t>
+          <t>必ず捨てるべき</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>砂糖</t>
+          <t>捨てずに活用すべき</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>発酵菌のみ</t>
+          <t>加熱してから捨てるべき</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>添加物</t>
+          <t>別の容器に移して廃棄すべき</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5446,32 +5446,32 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>記事はこの液体をどう扱うことを勧めているか？</t>
+          <t>記事が紹介している活用法の特徴は？</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>必ず捨てる</t>
+          <t>火を使わず短時間で作れる夏向きレシピ</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>捨てずに使い切る</t>
+          <t>何時間も煮込む必要があるレシピ</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>冷凍して廃棄する</t>
+          <t>オーブンが必須のレシピ</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>煮沸して捨てる</t>
+          <t>特別な機材が必要なレシピ</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5509,27 +5509,27 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>記事の中で紹介されている活用例に含まれるのは？</t>
+          <t>この記事が伝える食品ロス削減の視点として適切なのは？</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>火を使わず5分で作れる夏向きレシピ</t>
+          <t>『傷んでいそう』という見た目の印象だけで捨てず正体を知れば活用できる</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1時間煮込むスープ</t>
+          <t>少しでも変化があれば必ず廃棄すべき</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>オーブンで焼くケーキ</t>
+          <t>ヨーグルトの上澄みは工業用にしか使えない</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>長期熟成させる保存食</t>
+          <t>ホエーは人体に有害である</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5572,27 +5572,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>UberとWayveが自動運転配車を開始した都市は？</t>
+          <t>このロンドンでの自動運転配車サービスの運行方式は？</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ニューヨーク</t>
+          <t>完全無人での運行</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>ロンドン</t>
+          <t>安全確認の運転手(監視員)が同乗する運行</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>東京</t>
+          <t>遠隔操作のみでの運行</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>パリ</t>
+          <t>ロボットが同乗する運行</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -5635,27 +5635,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>このサービスは無人運転か？</t>
+          <t>このサービスの運行範囲について記事が説明しているのは？</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>完全無人</t>
+          <t>空港を含む全域</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>安全確認の運転手が同乗</t>
+          <t>空港を除く市内の一部で少数車両</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>遠隔操作のみ</t>
+          <t>郊外のみ</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>ロボットが同乗</t>
+          <t>高速道路のみ</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5761,32 +5761,32 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>東京での試験運行で連携予定とされる企業に含まれるのは？</t>
+          <t>この記事が示す自動運転サービス普及の現状として適切なのは？</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>日産自動車</t>
+          <t>すでに完全無人で世界中に普及している</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>トヨタ自動車</t>
+          <t>安全策を伴いながら段階的に実証が進んでいる</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>ホンダ</t>
+          <t>まだどこの国でも実施されていない</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>スズキ</t>
+          <t>日本ではすでに完全無人化されている</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5824,32 +5824,32 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ChatGPT Workの仕組みを分析したとされる人物は？</t>
+          <t>ChatGPT Workが持つとされる高度な機能として記事が挙げているのは？</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>サム・アルトマン氏</t>
+          <t>インターネット接続やサイト作成</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>サイモン・ウィリソン氏</t>
+          <t>音声通話機能のみ</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>イーロン・マスク氏</t>
+          <t>オフラインでの動作のみ</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>サティア・ナデラ氏</t>
+          <t>動画編集機能</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5887,32 +5887,32 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ChatGPT Workが持つとされる高度な機能に含まれるのは？</t>
+          <t>記事が指摘するChatGPT Workのリスクは？</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>インターネット接続やサイト作成</t>
+          <t>価格が高すぎること</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>動画編集</t>
+          <t>外部の悪意ある指示に操られる危険性</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>音声通話</t>
+          <t>日本語に対応していないこと</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>3Dモデリング</t>
+          <t>処理速度が遅いこと</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5950,27 +5950,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>記事が指摘するリスクは？</t>
+          <t>記事によれば、安全対策の全容はどう説明されているか？</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>価格が高すぎること</t>
+          <t>完全に公式確認されている</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>外部の悪意ある指示に操られる危険性</t>
+          <t>公式には未確認である</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>日本語に対応していないこと</t>
+          <t>第三者機関が保証済みである</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>処理速度が遅いこと</t>
+          <t>存在しないと明言されている</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>記事によれば安全対策の全容は？</t>
+          <t>この記事が示す教訓として適切なのは？</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>完全に公式確認されている</t>
+          <t>高度な機能には便利さとリスクの両面があり注意が必要</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>公式には未確認</t>
+          <t>高度な機能は常に安全だと保証されている</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>第三者機関が保証済み</t>
+          <t>AIの機能拡張にリスクは一切伴わない</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>存在しないと明言されている</t>
+          <t>この機能は誰も使うべきではない</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6076,32 +6076,32 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>遭難事故が起きた山はどこか？</t>
+          <t>当局が問題視したのは、AIのどのような助言だったか？</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>シャスタ山</t>
+          <t>ルート選択の誤り</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>富士山</t>
+          <t>食料や水を少なく持つよう勧めたこと</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>エベレスト</t>
+          <t>天候予測の誤り</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>ホイットニー山</t>
+          <t>装備の選び方</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6139,27 +6139,27 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>登山者が計画に利用したとされるAIは？</t>
+          <t>記事によれば、実際のAIの回答内容についてはどう説明されているか？</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>完全に確認され公開されている</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>実際の回答内容は確認されていない</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>AIが回答を否定している</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Copilot</t>
+          <t>裁判で証拠として採用された</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6202,32 +6202,32 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>当局が問題視したAIの助言内容は？</t>
+          <t>記事が指摘する、遭難にAIの助言以外で重なっていた要因は？</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ルート選択</t>
+          <t>推奨時刻を大幅に過ぎた行動や道迷い</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>食料と水を少なく持つよう勧めたこと</t>
+          <t>装備の完全な欠如</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>天候予測</t>
+          <t>悪天候のみ</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>装備の選び方</t>
+          <t>通信障害のみ</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6265,27 +6265,27 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>記事によれば、遭難にはAIの助言以外にどんな要因も重なっていたか？</t>
+          <t>この記事が伝える教訓として適切なのは？</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>推奨時刻を大幅に過ぎた行動や道迷い</t>
+          <t>AIの助言を鵜呑みにせず他の要因も含め慎重に計画を立てる必要がある</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>悪天候のみ</t>
+          <t>AIに登山計画を任せれば安全は完全に保証される</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>装備の故障のみ</t>
+          <t>AIは登山計画には一切使うべきではない</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>体調不良のみ</t>
+          <t>遭難の原因はAIの助言だけで説明できる</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6328,32 +6328,32 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Xが特定したとされるアカウント数はおよそ何件？</t>
+          <t>Xが特定したアカウントが投稿していた批判の対象は？</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>約2万</t>
+          <t>米国のAI向けデータセンター</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>約20万</t>
+          <t>中国の工場</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>約2百万</t>
+          <t>欧州の発電所</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>約2千</t>
+          <t>日本の半導体工場</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6391,27 +6391,27 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>このうち何件がAI施設への批判を投稿していたか？</t>
+          <t>記事によれば、これらの投稿が住民の反対世論を実際に広げたかについての根拠は？</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>約20件</t>
+          <t>明確に示されている</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>約200件</t>
+          <t>具体的な根拠は示されていない</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>約2,000件</t>
+          <t>完全に否定されている</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>約20,000件</t>
+          <t>第三者機関が証明した</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -6454,32 +6454,32 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>批判の対象とされたのは何か？</t>
+          <t>中国政府の指示があったかについて記事はどう述べているか？</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>米国のAI向けデータセンター</t>
+          <t>政府が公式に認めている</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>中国の工場</t>
+          <t>具体的な根拠は示されていない</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>欧州の発電所</t>
+          <t>裁判で立証された</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>日本の半導体工場</t>
+          <t>Xが断定している</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6517,32 +6517,32 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>記事によれば、中国政府の指示があったかについての根拠は？</t>
+          <t>この記事が示す情報の受け止め方として適切なのは？</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>明確に示されている</t>
+          <t>『疑われる』段階の情報であり断定はできないと理解する</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>具体的な根拠は示されていない</t>
+          <t>発表内容をそのまま断定的事実として受け取る</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>政府が公式に認めている</t>
+          <t>政治的な陰謀論として無視する</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>第三者機関が証明した</t>
+          <t>記事の内容は完全に立証済みとして扱う</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6580,27 +6580,27 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>GPT-6 Astraを使って動画の色調整を行ったと発表した企業は？</t>
+          <t>この記事で紹介されている技術は何を行うものか？</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Higgsfield AI</t>
+          <t>動画の色味を参考画像に合わせて調整する</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>動画の音声を自動生成する</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>動画の字幕を自動翻訳する</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Runway</t>
+          <t>動画の解像度を上げる</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6643,32 +6643,32 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>記事によれば、色味の調整にかかった時間は？</t>
+          <t>記事が指摘する、この発表の不確かな点は？</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>40分</t>
+          <t>所要時間(4分)が発表者側の主張であること</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>4分</t>
+          <t>動画自体が存在しないこと</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>14分</t>
+          <t>効果が全く確認できないこと</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>24分</t>
+          <t>技術が違法であること</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6706,32 +6706,32 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>色調整は何に合わせて行われたか？</t>
+          <t>記事によれば、AIとソフトをどう連携させたかという詳しい手順は？</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>参考画像</t>
+          <t>詳細に公開されている</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>過去の作品傾向</t>
+          <t>詳しくは明かされていない</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>AIの独自判断</t>
+          <t>特許として公開済み</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>ユーザーの好み診断</t>
+          <t>無料で誰でも試せる</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6769,27 +6769,27 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>記事が指摘する不確かな点は？</t>
+          <t>この記事から読み取れる、AI関連ニュースを見る際の姿勢として適切なのは？</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>所要時間が発表者の主張であること</t>
+          <t>発表内容と第三者による検証の有無を区別して捉える</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>動画の画質</t>
+          <t>発表された数字はすべて客観的事実として扱う</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>著作権の扱い</t>
+          <t>動画が公開されていれば主張はすべて正しい</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>価格設定</t>
+          <t>企業の発表を検証する必要はない</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -6832,27 +6832,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Microsoftが発表した新しい文字起こしAIの名称は？</t>
+          <t>Microsoftが自社評価として主張している新しい文字起こしAIの特徴は？</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>MAI-Transcribe-2</t>
+          <t>他社より速く正確で安価</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Azure Voice Pro</t>
+          <t>他社より遅いが高精度</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Copilot Speech</t>
+          <t>無料で永久に使える</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>MS-Text-1</t>
+          <t>日本語専用に開発された</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -6895,27 +6895,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>発表された日付は？</t>
+          <t>記事によれば、この特別価格が適用される期間は？</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026年8月3日</t>
+          <t>無期限</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026年9月3日</t>
+          <t>2026年末まで</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026年7月3日</t>
+          <t>発表から1ヶ月間</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026年10月3日</t>
+          <t>1週間限定</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -6958,32 +6958,32 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>自社評価によれば処理速度はGPTと比べてどうか？</t>
+          <t>記事が指摘する、この発表の限界は？</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>同程度</t>
+          <t>品質保証がなく日本語単独の精度も資料で確認されていない</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>半分</t>
+          <t>全ての主張が第三者機関で検証済み</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>10倍</t>
+          <t>価格が非常に高いこと</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2倍</t>
+          <t>全く実用化されていないこと</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7021,27 +7021,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>記事によれば特別価格の期限は？</t>
+          <t>この記事から読み取れる教訓は？</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026年末まで</t>
+          <t>自社評価による性能主張は独立した検証結果と同じではないと理解すべき</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>無期限</t>
+          <t>自社評価は常に客観的で信頼できる</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2027年末まで</t>
+          <t>価格が安ければ品質も保証される</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>発表から1ヶ月間</t>
+          <t>日本語対応は確認済みなので安心して良い</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -7084,27 +7084,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ダイソンが発売した電動歯ブラシの名称は？</t>
+          <t>Dyson CameraJetが搭載している技術は？</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Dyson CameraJet</t>
+          <t>内蔵カメラとAIで歯の隙間を検知し洗口液を噴射する</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Dyson AirClean</t>
+          <t>超音波で歯垢を破壊する</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Dyson SmartBrush</t>
+          <t>体温を測定する</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Dyson OralAI</t>
+          <t>音声でブラッシング状況を教える</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -7147,32 +7147,32 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>この歯ブラシの価格は？</t>
+          <t>「汚れの除去が最大69%増加」というデータについて記事が指摘している点は？</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>税込39,800円</t>
+          <t>人での使用試験の結果である</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>税込59,800円</t>
+          <t>ブラシ単独の実験室での試験結果であり人での試験結果ではない</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>税込79,800円</t>
+          <t>第三者機関による独立調査である</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>税込99,800円</t>
+          <t>数万人規模のユーザー調査である</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -7210,27 +7210,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>歯ブラシに内蔵されている技術は？</t>
+          <t>この製品は歯磨きと同時に何ができるとされているか？</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>内蔵カメラとAI</t>
+          <t>歯間ケア</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>超音波センサー</t>
+          <t>ホワイトニング</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>温度センサー</t>
+          <t>口臭測定</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>GPS</t>
+          <t>虫歯の検知</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -7273,32 +7273,32 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>「汚れの除去が最大69%増加」というデータの性質は？</t>
+          <t>この記事が伝える教訓として適切なのは？</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>人での使用試験の結果</t>
+          <t>企業発表の数値がどんな条件下で得られたものか確認することが重要</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>ブラシ単独の実験室試験結果</t>
+          <t>発表された数値はすべて実生活でそのまま再現される</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>第三者機関の独立調査</t>
+          <t>高価な製品は必ず効果が高い</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>ユーザーアンケート結果</t>
+          <t>AI搭載であれば効果は保証される</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Anthropicが限定公開した仕組みは何を調べるものか？</t>
+          <t>Anthropicが公開した仕組みが調べるのは何か？</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Claudeのバグ報告</t>
+          <t>ユーザーの個人情報</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -7399,17 +7399,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>この窓口は誰に限定公開されたか？</t>
+          <t>この窓口は誰に向けて公開されたか？</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>一般ユーザー全員</t>
+          <t>一般ユーザー全員に無制限公開</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>規制当局や教育機関など</t>
+          <t>規制当局や教育機関などに限定公開</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>株主のみ</t>
+          <t>競合AI企業のみ</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -7462,27 +7462,27 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>この技術で推定できるのは何か？</t>
+          <t>この技術で区別できないと記事が説明しているのは？</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Claudeが関わった確率</t>
+          <t>AIが全文を書いたか人の文章を大幅に直したか</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>文章の著作権者</t>
+          <t>日本語か英語か</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>文章の言語</t>
+          <t>文章の長さ</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>文章の感情分析</t>
+          <t>投稿された時間</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -7525,32 +7525,32 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>記事によれば、この技術で区別できないこととは？</t>
+          <t>この記事が伝える、AI生成物の判定技術の現状として適切なのは？</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>日本語か英語か</t>
+          <t>便利ではあるが万能ではなく限界がある</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>AIが全文を書いたか人の文章を大幅に直したか</t>
+          <t>完璧に判定でき限界は一切ない</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>文章の長さ</t>
+          <t>全く実用化されていない</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>投稿された時間</t>
+          <t>誰でも自由に使える一般公開ツールである</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7588,27 +7588,27 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>求職者が企業の選考で使わせたとされるAIは？</t>
+          <t>この事例で求職者が企業の選考にどう対応したか？</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>自動音声選考にChatGPTで応答させた</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>面接を辞退した</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>人間の代理人を立てた</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Copilot</t>
+          <t>選考を無視した</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -7651,32 +7651,32 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>このAIが対応したとされる選考の種類は？</t>
+          <t>この事例の結果として記事が伝えているのは？</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>自動音声選考</t>
+          <t>合格して採用された</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>筆記試験</t>
+          <t>企業からの連絡はなかった</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>グループディスカッション</t>
+          <t>即座に不合格通知が届いた</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>適性検査</t>
+          <t>追加面接に呼ばれた</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -7714,32 +7714,32 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>記事によれば、この事例の結果はどうだったか？</t>
+          <t>記事が注意を促しているポイントは？</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>合格した</t>
+          <t>AI同士が対話しても合格を意味しない</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>企業からの連絡はなかった</t>
+          <t>AIの声が不自然であること</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>即座に不合格通知が来た</t>
+          <t>費用がかかりすぎること</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>追加面接に呼ばれた</t>
+          <t>導入企業が少ないこと</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7777,27 +7777,27 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>記事が注意を促しているのはどんな点か？</t>
+          <t>この記事から読み取れる、AI面接の広がりに対する見方として適切なのは？</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AI同士が対話しても合格を意味しない</t>
+          <t>対話が成立すること自体が結果の保証にはならない</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>AIの声が不自然であること</t>
+          <t>AIが面接すれば必ず公平な結果になる</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>費用が高いこと</t>
+          <t>AI面接はもはや不要になった</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>導入企業が少ないこと</t>
+          <t>AI同士の対話は常に高評価につながる</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>OpenAIの人型ロボット開発を報じたメディアは？</t>
+          <t>記事によれば、OpenAIが自前で設計する方針とされているのは何か？</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Forbes JAPAN</t>
+          <t>AIソフトウェアのみ</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>日経新聞</t>
+          <t>頭脳となるAIだけでなく機体そのものも含む</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>朝日新聞</t>
+          <t>充電インフラのみ</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>TechCrunch Japan</t>
+          <t>販売網のみ</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -7903,27 +7903,27 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>OpenAIが自前で設計する方針とされているのは何か？</t>
+          <t>まず活用を目指しているとされる現場は？</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AIソフトウェアのみ</t>
+          <t>家庭用</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>機体そのものも含む</t>
+          <t>製造業などの現場</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>充電インフラのみ</t>
+          <t>医療現場のみ</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>販売網のみ</t>
+          <t>教育現場のみ</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -7966,32 +7966,32 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>まず活用を目指しているとされる現場は？</t>
+          <t>記事において、将来的な展望として描かれているのは？</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>家庭用</t>
+          <t>個人向けへの普及</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>製造業などの現場</t>
+          <t>軍事利用のみ</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>医療現場のみ</t>
+          <t>完全に非公開の研究のみ</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>教育現場のみ</t>
+          <t>販売の予定はない</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -8029,32 +8029,32 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>記事において出荷時期は？</t>
+          <t>記事における出荷時期や具体的な試作機についての説明は？</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026年内</t>
+          <t>明確に示されている</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2027年前半</t>
+          <t>示されていない</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>示されていない</t>
+          <t>すでに出荷が始まっている</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2028年</t>
+          <t>試作機は完成し公開済み</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>

--- a/data/quiz/quiz_bank.xlsx
+++ b/data/quiz/quiz_bank.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -429,6 +429,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,6 +498,11 @@
           <t>correct</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -560,6 +566,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>娯楽(342分)や仕事(228分)と比べて、お金の管理に使われていた時間は1日わずか8.3分だった。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -623,6 +634,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>幸福感を0〜6点で評価してもらったところ、お金の管理をしている人の多くは低い点数をつけ、嫌いだと感じていた。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -686,6 +702,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>タイトル自体が「金持ちほど管理に時間を使うのに、なぜストレスは少ないのか」という一見矛盾した現象を問いかけている。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -749,6 +770,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>使う時間の長さとストレスの大小は単純には比例していない、というのがこの調査から読み取れる示唆。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -812,6 +838,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>体質によってホルモン補充療法が使いにくい人向けにサプリを補足的に紹介しつつ、記事は最有力の方法として明記している。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -875,6 +906,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>表の中で大豆イソフラボンは「効果は小さいが、比較的データが多い」と評価されている。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -938,6 +974,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>レッドクローバーは「結果が割れている」と評価されている。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1001,6 +1042,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>成分ごとに「効果の大きさ」と「データの量」が異なるため、記事は一律に良し悪しを言わず見極めが必要という立場をとっている。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1064,6 +1110,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>研究は「出勤で得られる雑談の喪失は、在宅勤務のメリットを上回るデメリットだ」という結論を出している。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1127,6 +1178,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>記事は「出勤における最大のメリットは雑談だ」と明記している。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1190,6 +1246,11 @@
           <t>C</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>研究はハイブリッド勤務をしている会社員を対象に、日々の働き方と心理状態を追跡したもの。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1253,6 +1314,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>偶発的な会話(雑談)のような定量化しづらい価値を軽視すべきでない、という含意がある。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1316,6 +1382,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>「更新が多くて、気になる記事を見逃してしまう」という悩みが読者から寄せられていたと書かれている。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1379,6 +1450,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ダイジェストは「前の週に公開した記事」を毎週まとめて届けるサービス。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1442,6 +1518,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>「毎週月曜日にまとめてお届けする」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1505,6 +1586,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>「あとで読もうと思った記事ほど忘れがち」という問題を解消する狙いがある。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1568,6 +1654,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>メタ分析は「恋人がいる人や独身者」と比較して、セフレ(FWB)関係の特徴を調べたもの。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1631,6 +1722,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>結果として「気楽で安全な面」と「健康上のリスクが高い面」の両方があったと記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1694,6 +1790,11 @@
           <t>D</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>調べられた5項目は性的行動・満足度、性感染症等の健康リスク、暴力・攻撃性、不安やうつ、孤独感・嫉妬で、仕事のパフォーマンスは含まれない。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1757,6 +1858,11 @@
           <t>C</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>「気楽で安全な面とリスクが高い面の両方」という表現は、単純な善悪二元論ではなく複雑な実態を描いている。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1820,6 +1926,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>タイトルの「量より機能」は、関係の「数」ではなく、その関係が果たす役割・機能に注目すべきという意味。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1883,6 +1994,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Lifestyle+では食事・運動・睡眠に加え「社会的孤立と孤独」が健康寿命に関わる要素として扱われている。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1946,6 +2062,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>記事は冒頭で「孤独と社会的孤立は同じではない」という区別を押さえるべきだと述べている。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2009,6 +2130,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>「人間関係の機能」に目を向けて孤独対策を考える、というのがこの回のテーマ。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2072,6 +2198,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>記事は「恋人がいない人の特性とは？」という問いを世界のデータから調べている。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2135,6 +2266,11 @@
           <t>D</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>分析では年齢・性別・学歴・収入・仕事の有無・文化的背景が比較要因として使われ、血液型のような項目は出てこない。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2198,6 +2334,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>記事冒頭で「収入があればモテる」「コミュ力があればいい」という俗説が紹介されている。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2261,6 +2402,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>「実際にどこまで個人のスペックが重要なのかまだよくわからない」という前置きから、単純な要因では説明しきれない可能性を示唆している。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2324,6 +2470,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>記事は「画像生成AIは消費者心理までは学んでいない」と明記している。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2387,6 +2538,11 @@
           <t>D</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>AIDAはAttention(注意)・Interest(興味)・Desire(欲求)・Activation(購入行動)の4段階で、「忘れさせる」は含まれない。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2450,6 +2606,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>記事は「売れる広告のコツは学習できる」と結論づけている。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2513,6 +2674,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>AIDAのような枠組みを使えば、AIでも効果的な広告を作れる可能性があるという実証的な内容。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2576,6 +2742,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>「ニオイや汗、ベタつき、乾燥などの小さな違和感が重なると、脳のメモリを奪う『状態ノイズ』になる」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2639,6 +2810,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>「強い香りでニオイを隠すのではなく、肌のコンディションを整えることで状態ノイズを減らす」商品だと説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2702,6 +2878,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>記事は「肌の乾燥は状態ノイズの大きな原因になる」と述べている。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2765,6 +2946,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>根本原因(肌コンディション)にアプローチする発想が、この商品コンセプトの核になっている。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2828,6 +3014,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>「慢性的なストレスは、がんの進行や転移を促す」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2891,6 +3082,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>記事は「ストレスには良いものと悪いものがある」と2種類に分けている。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2954,6 +3150,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Lifestyle+は食事・運動・睡眠(+孤独対策)を健康寿命の要素として扱っている。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3017,6 +3218,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>タイトル通り「同じストレス対策でも人によって効き方が違う」という個人差がテーマ。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3080,6 +3286,11 @@
           <t>C</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>記事は「水にさらすと揚げたときにできるアクリルアミドが減る」という、くっつき・変色防止以外の理由を強調している。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3143,6 +3354,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>「冷蔵庫で保存したじゃがいもは揚げ物に向かない」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3206,6 +3422,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>「揚げ色は薄い黄金色で止めるのが正解」とされている。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3269,6 +3490,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>水にさらす・保存状態・揚げ色という3つの根拠が、いずれもアクリルアミド低減という安全性につながっている。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3332,6 +3558,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>「むいたつもりでも皮はまだ残っている」ことが丸まる原因で、身に密着した第3・4層が加熱で縮むため。</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3395,6 +3626,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>「手でむける茶色い皮は表面の1〜2層だけ」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3458,6 +3694,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>「身に密着した透明な第3・4層はそのまま残っている」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3521,6 +3762,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>タイトル通り「切り込みひとつでやわらかく仕上がる」という対策が紹介されている。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3584,6 +3830,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>「あの白いものは水に溶けるたんぱく質『アルブミン』です」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3647,6 +3898,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>パルシステムの解説を引用し「無害で、食べても問題ない」とされている。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3710,6 +3966,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>「焼く前の塩水10分」で防げると紹介されている。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3773,6 +4034,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>見た目が気になる現象(白い汁)も、仕組み(アルブミンの凝固)がわかれば対処できる、という構成になっている。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3836,6 +4102,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>「重曹が酸に触れると酸塩基反応が起き、二酸化炭素と水ができる。この泡が生地を押し広げる」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3899,6 +4170,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>「加熱だけで分解すると同時に炭酸ナトリウムが生地に残る」とされている。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3962,6 +4238,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>炭酸ナトリウムは「アルカリが強く、独特の苦みや塩気、黄色っぽい色の原因になる」とされ、焼き色も濃くなる。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4025,6 +4306,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>タイトル通り「重曹は酸と組ませて使う」ことで本領を発揮する、というのが記事の教訓。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4088,6 +4374,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>「粒子表面がマイナスに帯電しており、同じ電荷同士は反発するため粒子はくっつかずバラバラのまま浮いている」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4151,6 +4442,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>「マグネシウムイオン(Mg2+)はプラスの電荷を持ち」粒子の反発を打ち消して凝集させる、という仕組みが説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4214,6 +4510,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>記事タイトルの通り「豆腐は電子レンジで作れる」という手軽さがテーマ。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4277,6 +4578,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>身近な化学(コロイドの凝集)を理解すれば、家庭でも再現できるという内容。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4340,6 +4646,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>「今週のひとこと総括」で「同じ材料でも、まわりの条件が味と栄養を変える」とまとめられている。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4403,6 +4714,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>「ケージ卵はコク」と紹介されている。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4466,6 +4782,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>「平飼い卵はうま味と甘み」と紹介されている。</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4529,6 +4850,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>総括で「台所で一番安く試せる変数は、案外そこ(環境)なのかもしれません」と述べられている。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4592,6 +4918,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>「原因のほとんどは火の強さです」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4655,6 +4986,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>「牛乳の主役たんぱく質はカゼインです」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4718,6 +5054,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>「骨組みをつなぐ接着剤=リン酸カルシウム」で、メルト性はこの接着剤の残存量で決まるとされている。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4781,6 +5122,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>タイトル通り「チーズソースは火を止めてから溶かす」ことで分離を防げるという教訓。</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4844,6 +5190,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>「切り離されたあとも呼吸を続け、細胞の中では酵素が働き続けている」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4907,6 +5258,11 @@
           <t>D</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>「光、温度、酸素にさらされるほど分解は速い」とあり、冷凍保存はむしろ分解を止める側の要因。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4970,6 +5326,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>「冷凍野菜は、その時計を畑で止めている」という表現が使われている。</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5033,6 +5394,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>「生の方が体にいい」という思い込みを、収穫後も進む栄養分解という観点から問い直している。</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5096,6 +5462,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>「家庭の煮る・蒸すという加熱では、その変化はほとんど起きていません」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5159,6 +5530,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>「主役はジンゲロール(6-ジンゲロール)、ピリッと立ち上がる辛味の正体」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5222,6 +5598,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>「加熱しなきゃ意味がないという縛りが外れるから」実用的な情報だとしている。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5285,6 +5666,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>加熱してもほぼ変化しないなら、生のままでも使い方の面で大差ないというのが実践的な教訓。</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5348,6 +5734,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>「あの液体は水ではありません。名前は『ホエー(乳清)』。牛乳の栄養がぎゅっと溶けこんだ食べ物」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5411,6 +5802,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>「捨てずに使い切る具体的な方法」を紹介する内容になっている。</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5474,6 +5870,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>「火を使わず5分で作れる夏向きのレシピ」が紹介されている。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5537,6 +5938,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>「傷んだのかな」という思い込みを、ホエーの正体を知ることで「使えるもの」に変える、という構成。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5600,6 +6006,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>「無人ではなく安全確認の運転手が同乗し」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5663,6 +6074,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>「空港を除く市内を少数の車両で走ります」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5726,6 +6142,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>「2026年後半には、日産自動車や日の丸交通と連携し、東京でも試験運行を行う計画」とされている。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5789,6 +6210,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>安全監視員同乗という段階を踏みながら地域を絞って進めている、段階的な実証という位置づけ。</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5852,6 +6278,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>「インターネット接続やサイト作成などの高度な機能を持つ」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5915,6 +6346,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>「外部の悪意ある指示に操られる危険性も指摘されています」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5978,6 +6414,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>「安全対策の全容は公式には未確認です」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6041,6 +6482,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>便利な機能とリスクが並記されており、利用にあたって両面を理解する必要があることを示している。</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6104,6 +6550,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>「事前の計画でGeminiに頼り、食料や水を少なく持つよう助言されたことを問題視」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6167,6 +6618,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>「実際のAIの回答内容は確認されておらず」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6230,6 +6686,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>「推奨時刻を大幅に過ぎた行動や道迷いも重なっていました」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6293,6 +6754,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>AIの助言だけでなく、行動の遅れや道迷いなど複数の要因が重なった結果として描かれている。</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6356,6 +6822,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>「米国のAI向けデータセンター批判を投稿していた」アカウントが対象とされている。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6419,6 +6890,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>「投稿が住民の反対世論を実際に広げたかや…具体的な根拠は示されていません」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6482,6 +6958,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>「中国政府が指示したかなどの具体的な根拠は示されていません」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6545,6 +7026,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>「疑う」「特定した」という段階の情報であり、断定的な事実として扱うべきではないことを示唆している。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6608,6 +7094,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>「参考画像に合わせて動画の色味を整える作業」を行う技術だと説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6671,6 +7162,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>「所要時間は発表者の主張です」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6734,6 +7230,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>「AIとソフトをどう連携させたかなど詳しい手順は明かされていません」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6797,6 +7298,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>企業発表の主張と、第三者が検証できる事実とを区別して読む姿勢が求められる内容。</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6860,6 +7366,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>「他社より速く正確で安価と同社は主張しています」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6923,6 +7434,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>「特別価格は2026年末まで」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6986,6 +7502,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>「品質保証もありません」「日本語単独の精度は今回の資料では確認されていません」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7049,6 +7570,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>自社評価による主張は独立した第三者検証とは異なる、という慎重な読み方が必要という教訓。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7112,6 +7638,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>「内蔵カメラとAIで歯と歯の間を見つけて液体を自動噴射する」機能だと説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7175,6 +7706,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>「ブラシ単独による実験室での試験結果であり、人での使用試験の結果ではありません」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7238,6 +7774,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>「歯磨きと同時に歯間ケアができる」とされている。</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7301,6 +7842,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>発表数値がどんな条件(実験室 vs 実使用)で得られたかを確認する重要性を示している。</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7364,6 +7910,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>「Claudeが生成した文章の『電子透かし』を調べる窓口」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7427,6 +7978,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>「規制当局や教育機関などに限定公開しました」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7490,6 +8046,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>「AIが全文を書いたのか、人の文章をAIが大幅に直したのかは区別できません」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7553,6 +8114,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>「確率を推定するもの」であり完全な判定ではない、という限界が明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7616,6 +8182,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>「企業の自動音声選考に音声対話AIのChatGPTで応答させた」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7679,6 +8250,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>「AI同士の会話は成立したものの企業からの連絡はありませんでした」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7742,6 +8318,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>「AI同士が対話しても合格を意味しない点に注意が必要」と明記されている。</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7805,6 +8386,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>対話が成立すること自体が採用の保証にはならない、という注意喚起。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7868,6 +8454,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>「頭脳となるAIだけでなく機体そのものも自前で設計する方針」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7931,6 +8522,11 @@
           <t>B</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>「まずは製造業などの現場での活用を目指し」と説明されている。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7994,6 +8590,11 @@
           <t>A</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>「将来的な個人向け普及を描いています」とある。</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -8055,6 +8656,11 @@
       <c r="M121" t="inlineStr">
         <is>
           <t>B</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>「出荷時期や具体的な試作機は今回の記事では示されていません」と明記されている。</t>
         </is>
       </c>
     </row>

--- a/data/quiz/quiz_bank.xlsx
+++ b/data/quiz/quiz_bank.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quiz_bank" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="psychology_bonus" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8667,4 +8668,1738 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>day_index</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>article_title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>article_url</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>published_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>choice_a</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>choice_b</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>choice_c</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>choice_d</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>陰キャの生きる道#1「陰キャの要因１．内向性」</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2206013</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>この記事で著者は「陰キャ」という言葉についてどう述べているか？</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>明確な学術的定義があり、心理学の研究対象になっている</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>明確な定義はなく、学術的な研究対象にもなっていない</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>医学的な診断基準が存在する</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>海外にしか存在しない概念である</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>記事は「そもそも『陰キャ』って言葉には明確な定義はないし、当然アカデミズムの研究対象になっておりません」と明記している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>陰キャの生きる道#2「陰キャの要因２．低い社会的自尊心」</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2206081</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>「低い社会的自尊心」の人に見られる傾向として記事が挙げているのは？</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>新しい人間関係や挑戦に積極的になる</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>新しい人間関係や挑戦に消極的になる</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>常に自信満々に振る舞う</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>他人の評価を全く気にしない</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>「自分の行動は結果に繋がらない」と感じているため、新しい人間関係や挑戦に消極的になると説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>陰キャの生きる道#3「陰キャの要因３．回避性パーソナリティ」</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2206601</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>「回避性パーソナリティ」の特徴として記事が説明しているのは？</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>社交を避けながらも、本心では他人に認められたいと思っている</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>誰からも認められたいと思わない</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>常に人前に出ることを好む</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>感情を全く持たない</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>「人前で注目を浴びたいが、社交を避けてしまう」「本心では他人から認められて成功したいと思っている」と説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>陰キャの生きる道#4「陰キャの要因4〜5.非主張性、依存的自己価値感」</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2206752</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>「非主張性」が高い人に見られるコミュニケーションの特徴は？</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>自分の意見を強く主張し他者を圧倒する</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>自分の意見を言えず沈黙したり不当な扱いに抗議しない</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>常に他人と対立する</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>感情を全く表に出さない</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>非主張的なコミュニケーションスタイルは「沈黙したり、不当な扱いを受けても抗議しなかったり、自分の価値や意見を過小評価しちゃったり」する特徴があるとされている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>陰キャの生きる道#5「陰キャの要因6〜7.現実逃避的傾向、慎重性」</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2206902</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>記事が説明する「現実逃避的傾向」とはどんな行動か？</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>日常のストレスから逃れるため、別の活動や空想の世界に没頭しすぎること</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>現実を直視し問題に真正面から取り組むこと</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>常に他人に助けを求めること</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>感情を分析すること</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>「日常のストレスや困難から逃れるために、別の活動や空想の世界に没頭しまくるような行動」で、「行き過ぎると人間関係が犠牲になってしまう」と説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>陰キャの生きる道#6「陰キャの要因8.虚脱感」</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2207151</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>記事が説明する「虚脱感(Languishing)」とはどんな状態か？</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>はっきりした鬱の状態</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>明確な鬱ではないが、幸福感や活力が欠けた無気力な状態</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>過剰に興奮している状態</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>完全に健康な状態</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>「はっきりとした鬱でもないけれど、幸福感や活力が欠けたような状態」で、放置するとメンタルヘルスの低下を招くと説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>陰キャの生きる道#7「陰キャの要因9.刺激追求性の低さ」</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2207401</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>「刺激追求性の低さ」という特性について記事はどう評価しているか？</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>百害あって一利なしの悪い特性である</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>悪い面だけでなく良い面も多い特性である</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>病気として治療が必要である</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>現代社会には存在しない特性である</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>「この特性については『百害あって一利なし』ってわけじゃなくて、良いところも非常に多かったりはします」と述べ、酒やギャンブル、危険な行動に近寄りにくい利点を挙げている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>陰キャの生きる道#8「陰キャの要因10．HSP」</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2208053</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>記事が説明する「HSP」の特徴は？</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>外的な刺激に鈍感で環境の変化に気づきにくい</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>外的な刺激に敏感で、感情や環境の変化を強く感じる</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>感情を一切感じない</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>常に外向的に振る舞う</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>「外的な刺激にめっちゃ敏感で、感情や環境の変化を強く感じる特性を持った人」と説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>陰キャの生きる道#9「陰キャの要因11．自閉症スペクトラム」</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2208130</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>記事が説明する「HFA(高機能自閉スペクトラム症)」とは？</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>正式な医療用語で、自立した生活が困難な状態を指す</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>正式な医療用語ではないが、自立した生活を送れるASD成人を指す通称</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ASDとは全く別の疾患</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>子どもにしか使われない用語</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>「正式な医療用語ではないんだけど、自立した生活を送ることができる自閉スペクトラム症(ASD)の成人を指す際によく使われております」と説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>陰キャの生きる道#10「内向型の陰キャが成功するための6ステップ」</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2208944</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>記事によれば、内向的な人が仕事の世界で陥りがちな思考は？</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>「自分には社交など無理なのだ」と思い込みがち</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>常に自信満々である</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>外向的な人を見下しがち</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>全く悩みを感じない</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>「仕事の世界ではそうした外向的な特性が重視されるので、私たち内向人間は『自分には社交など無理なのだ！』と思いがち」と説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>偏見や先入観で誤った判断をしないための５つのユーザーズガイド</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/1405642456705811162</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2015-03-19</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>記事が紹介する「メンタルタイムトラベル」というバイアス対策のコツは？</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>バラ色の未来を想像する</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>あえてダークな(失敗した)未来を想像する</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>過去の成功体験だけを思い出す</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>未来について一切考えない</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>「バラ色の未来を想像しても意味がないので、あえてダークな光景をイメージするのがコツ」とされ、いまの決断が失敗に終わった未来を想像するとよいと説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>私たちの判断を鈍らせる「認知のゆがみ」40選</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/4881377405297836617</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2016-06-27</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>記事が紹介する「読心」という認知のゆがみとは？</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>他人が思ってそうなことを勝手に推測すること</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>他人の考えを正確に読み取る特殊能力</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>自分の考えを他人に伝えること</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>読書をして知識を深めること</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>「読心」は「他人が思ってそうなことを勝手に推測」する認知のゆがみの例として挙げられ、「この人はわたしを嫌っている！」のような思考が例示されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ほんの１時間のトレーニングでも「確証バイアス」ってそこそこ解除できるんだなぁ……という実験</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/8413847968646882215</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2019-10-27</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>記事が紹介する実験で、確証バイアスを軽減させるために行われたことは？</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>被験者の半分に専用のゲームをプレイしてもらった</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>被験者全員に薬を投与した</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>被験者に長期間の瞑想をさせた</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>何も介入せず自然に軽減するのを待った</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>HEC経営大学院の実験で、「被験者の半分に『バイアス解除用』のゲームをプレイしてもらう」という方法が取られたと説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>「本当の自己分析」って超ムズいから、原因を押さえておこうぜ！#2「スポットライト効果」</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/3451203365615573037</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>記事が紹介する「マイノリティへの意識過剰」というバイアスの例として挙げられているのは？</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>子どもたちは自己紹介で自分のマジョリティ側の特徴ばかり挙げる</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>子どもたちは自己紹介で自分のマイノリティな側面(髪の色や出身地など)を挙げがち</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>大人だけに見られる現象である</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>全く実証されていない仮説である</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ウィリアム・マクガイアの研究によれば、子どもたちに自己紹介をさせると「ほとんどが自分のマイノリティな側面を挙げた」とされ、赤毛の子は髪の色を、外国生まれの子は出身地を挙げる例が示されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>「初対面の人の会話がうまくいかなくて……」を克服するための心理学</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/5500911324669696199</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2018-09-22</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>記事が紹介する研究が示した、人間関係における私たちのバイアスとは？</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>自分は他人から好かれやすいと思い込みがち</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>自分は他人から好かれないのだと思い込みがち</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>他人の好意を完璧に見抜ける</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>初対面では誰にでも緊張しない</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>「どうやら人間には『自分は他人から好かれないのだ……』と思いやすいバイアスがあるらしいぞ」という研究結果が紹介されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>バイアスを乗り越えて正しい意思決定を行うための12の質問 #1 前半戦</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/1796296</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2019-08-17</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>記事によれば、カーネマン先生が指摘した問題点は？</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>誰もバイアスの存在を知らない</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>みんなバイアスの影響を知っているのに日常の意思決定に活かしていない</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>バイアス対策をしても全く効果がない</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>バイアスは意思決定に一切影響しない</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>カーネマンは「みんなバイアスの影響は知ってるくせに、日常の意思決定に活かしてないじゃないか」と指摘していると紹介されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>マインドフルネス VS.認知行動療法　勝つのはどっちだ！みたいな実験</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/4870926240773507343</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2016-07-16</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>記事によれば、マインドフルネスの効果について現時点で言えることは？</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>不安やうつへの効果はほぼ間違いないが、集中力向上などの効果はまだデータ不足</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>すべての効果が完全に実証されている</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>全く効果が確認されていない</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>認知行動療法より明確に劣ることが証明されている</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>「現時点だとうつや不安に効くのはほぼ間違いないんだけど、いっぽうで集中力アップとか仕事の効率改善とか、ライフハックっぽい目的で使えるかはまだデータ不足」と説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>先延ばしの正体は「やる気不足」とは関係ないから、もっと感情にフォーカスしようぜ！という研究の話</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/8749131252631180303</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>この記事が紹介する研究の視点として適切なのは？</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>先延ばしは単なる「やる気不足」で説明できる</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>先延ばしは感情の動きに着目することで理解が深まる</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>先延ばしは遺伝だけで決まる</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>先延ばしは現代特有の新しい現象である</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>タイトル通り「先延ばしの正体は『やる気不足』とは関係ないから、もっと感情にフォーカスしよう」という視点で、タスクへの感情とその後の行動・感情変化を追跡した研究が紹介されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>マジメな人ほどハマりがちなスケジュール管理の罠「プレクラスティネーション」</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/3639977383355488178</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2014-07-15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>記事が紹介する「プレクラスティネーション」とはどんな傾向か？</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>準備ができていなくてもすぐにタスクに取りかかってしまう傾向</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>タスクを完全に先延ばしにする傾向</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>全くタスクに取り組まない傾向</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>他人にタスクを押し付ける傾向</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>「先延ばし(procrastination)」をもじった言葉で、「ちゃんとした準備もできてないのにガンガンとタスクをこなしていくメンタリティ」と説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>「先延ばし」について徹底的に考えてみよう！#5「衝動編」</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/1911270</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2020-06-18</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>記事が説明する「衝動」による先延ばしとはどんなパターンか？</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>長期的な利益より目先の短期的な喜びを優先してしまうパターン</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>長期的な利益だけを常に優先するパターン</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>衝動的な行動を一切取らないパターン</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>感情に全く左右されないパターン</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>「長期的な利益よりも短期的な喜びに意識をジャックされて、目先の喜びに耽溺するパターン」と説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>「先延ばし」について徹底的に考えてみよう！#2「未来感覚編」</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/1898214</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2020-05-19</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>記事が指摘する、先延ばしの原因についての重要なポイントは？</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>原因はすべての人で同じであり対策も一律でよい</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>原因は人によって千差万別なので自分の原因を理解する必要がある</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>先延ばしに原因はなく偶然起きる</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>やる気さえあれば誰でも解決できる</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>「原因は千差万別」であり、「まずは『自分はどんな理由で先延ばしをしてるのか？』を理解する」ことが先決だと説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>「すぐやる人」が意外と損をしちゃうのはなぜか？──“プレクラステネーション”問題を考える</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/5219068783081691260</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>記事によれば「プレクラステネーション」がもたらしうる問題は？</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>常に効率的で問題が起きることはない</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>無駄な努力や判断ミスにつながり、先延ばしより厄介な場合もある</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>先延ばしと全く同じ結果しかもたらさない</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>心理学的には全く研究されていない</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>「このプレクラステネーションは無駄な努力や判断ミスにつながりやすく、ときに先延ばしよりも厄介な問題を引き起こすことがある」と説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>やるべき仕事を先延ばししちゃうなあ……の最大原因と、その解決方法のお話</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/6591089539981605535</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2022-02-28</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>記事が紹介する、先延ばしの最も有力な原因は？</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>単なる時間管理能力の不足</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ネガティブな感情に対処するための回避行動</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>遺伝的な要因のみ</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>タスクの量が多すぎること</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>「先延ばしは感情の問題である」というのが最も有力で、「私たちは、ネガティブな感情に対処するために先延ばしをする」と説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>仕事をつい先送りしちゃう！を引き起こす7つの感情要因と、その対策</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/6816130817205520146</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2017-10-23</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>記事が紹介するピチル博士の説は？</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ポジティブな感情が増えるほど先延ばしをしたくなる</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ネガティブな感情が増すほど先延ばしをしたくなる</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>感情は先延ばしと無関係である</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>先延ばしは意志力だけで説明できる</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ピチル博士は「ネガティブな感情が増すほどヒトは目の前の仕事を先送りしたくなるのだ」という説を唱えていると紹介されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>カールトン大学流、先延ばし克服のための４ステップ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2326675908603132353</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2014-07-11</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>記事が紹介する先延ばし克服のステップ1は何か？</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>まず自分が先延ばしをしていることに気づく</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>いきなり長時間作業する</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>他人に代わりにやってもらう</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>目標を立てずに行動する</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>「先延ばしに気づく」ことが最初のステップとされ、「自分がやるべき作業を決めておき、そこから気が逸れたら、そのときの思考」に気づくことが重要だとされている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>「自信がない！」を改善するメンタルテク「コンパッションゴール」</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/4703778248960394566</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2017-11-21</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>記事によれば、自尊心の低さと鬱の関係についての心理学界のコンセンサスは？</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>自尊心が低いほど鬱になりやすい</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>自尊心の高さと鬱は無関係である</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>自尊心が高いほど鬱になりやすい</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>自尊心は鬱の症状に一切影響しない</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>「自尊心が低い人ほど鬱になりやすいってメタ分析があったりします」と紹介されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>健康になるために欠かせない「自己効力感」を判断する8つの質問</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/7740540291959725106</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2018-07-23</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>記事が説明する「自己効力感」と「自尊心」の関係は？</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>全く同じ概念である</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>自己効力感は『できる』という感覚で、自尊心とは別の概念である</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>自尊心の方が新しい概念である</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>自己効力感は健康には全く影響しない</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>「自己効力感」は「これぐらいならできるっしょ」という感覚のことで、「無条件で自分には価値があるのだ」と考える「自尊心」とはまた別の概念だと説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>不安や鬱よりも「自尊心の低さ」のほうが人生を壊すかもしれないぞ！というデータ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2398669174835369260</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2019-02-05</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>記事が紹介する研究の結論として適切なのは？</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>不安や鬱よりも自尊心の低さの方が人生への悪影響が大きい可能性がある</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>自尊心は人生に全く影響しない</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>不安や鬱の方が自尊心の低さより明らかに悪影響が大きい</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>自己破壊的行動と自尊心は無関係である</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>タイトル通り「不安や鬱よりも『自尊心の低さ』のほうが人生を壊すかもしれない」という結論が紹介されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>成功の鍵は“他人を褒めること”！地位不安から自由になる心理学</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/2639907756269661027</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>記事が紹介する「地位不安」とはどんな心理か？</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>自分の地位や評価が不安定だと感じ、功績を限られた資源のように捉えてしまう心理</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>常に自分の地位に満足している心理</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>他人を褒めることに全く抵抗がない心理</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>地位や評価に一切関心がない心理</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>「『自分の評価や立場は不安定だよなぁ……』と感じる」ことから「『地位』や『功績』は限られた資源だ」と感じてしまう心理として「地位不安」が説明されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ナルシストと自信がある人ってなにが違うの？というか本当の自信ってなに？問題</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://daigovideolab.jp/blog/3926533781265641786</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2017-12-21</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>記事が指摘する、ナルシストと本物の自信がある人の違いの出発点は？</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>両者は完全に同じものである</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>一見同じように見えるが、実際には異なる心理状態である</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ナルシストの方が必ず幸福度が高い</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>自信がある人には必ずナルシシズムが含まれる</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>「一見したところでは、ナルシシズムと自尊心は同じように思える」が、研究チームは過去の研究をレビューし「両者の差をハッキリさせようと試みて」いると説明されている。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>